--- a/data/trans_orig/IPAQ_MET-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>73261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107955</t>
+          <t>106451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102534</t>
+          <t>101063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141032</t>
+          <t>139351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119609</t>
+          <t>120359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154496</t>
+          <t>156866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141025</t>
+          <t>140712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173124</t>
+          <t>174482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271101</t>
+          <t>269238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319986</t>
+          <t>319292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,82%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>52126</t>
+          <t>51924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82295</t>
+          <t>81055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>83523</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117643</t>
+          <t>116595</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>144874</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>189052</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54741</t>
+          <t>53843</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85362</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>35768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>77117</t>
+          <t>76895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112039</t>
+          <t>114220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>259286</t>
+          <t>259021</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>302444</t>
+          <t>303213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249914</t>
+          <t>249643</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>299096</t>
+          <t>299171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>520814</t>
+          <t>520358</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>585854</t>
+          <t>589015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>132677</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174925</t>
+          <t>172614</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200190</t>
+          <t>202113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246862</t>
+          <t>248674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344650</t>
+          <t>345627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409250</t>
+          <t>409899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,96%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27996</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50976</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18810</t>
+          <t>17436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>37590</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63435</t>
+          <t>62945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165212</t>
+          <t>164831</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199128</t>
+          <t>200642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178889</t>
+          <t>179711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214131</t>
+          <t>215398</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>354377</t>
+          <t>353408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>404878</t>
+          <t>403801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82591</t>
+          <t>81987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>114754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111385</t>
+          <t>110681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146129</t>
+          <t>145478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202858</t>
+          <t>201151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251053</t>
+          <t>250115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47497</t>
+          <t>49143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76670</t>
+          <t>80288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>20864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42588</t>
+          <t>43442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75661</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113433</t>
+          <t>112276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196447</t>
+          <t>194228</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234944</t>
+          <t>234042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>174911</t>
+          <t>173168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215040</t>
+          <t>213418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378812</t>
+          <t>381636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439951</t>
+          <t>439587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77118</t>
+          <t>77311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112228</t>
+          <t>110882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>140979</t>
+          <t>144100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181885</t>
+          <t>183545</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>229516</t>
+          <t>227214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>283428</t>
+          <t>281960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36475</t>
+          <t>36527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61728</t>
+          <t>63085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>74113</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102424</t>
+          <t>102191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>65955</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93706</t>
+          <t>95300</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148967</t>
+          <t>147766</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>186990</t>
+          <t>188302</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77258</t>
+          <t>77938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105436</t>
+          <t>107155</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107712</t>
+          <t>107114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135793</t>
+          <t>136801</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193607</t>
+          <t>192504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>234976</t>
+          <t>234589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56847</t>
+          <t>56673</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111280</t>
+          <t>111405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143770</t>
+          <t>144499</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108552</t>
+          <t>110784</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143641</t>
+          <t>144185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>230992</t>
+          <t>229940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>278104</t>
+          <t>275921</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>91728</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125039</t>
+          <t>124295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115127</t>
+          <t>115473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148990</t>
+          <t>148240</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>216284</t>
+          <t>215567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>263081</t>
+          <t>261189</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>75097</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110189</t>
+          <t>113967</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>34816</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>62914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>115190</t>
+          <t>116151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>160041</t>
+          <t>163578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>265571</t>
+          <t>267181</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>320031</t>
+          <t>322340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>304158</t>
+          <t>303691</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>356492</t>
+          <t>360780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>585299</t>
+          <t>586004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>662407</t>
+          <t>664961</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>243066</t>
+          <t>240925</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>296894</t>
+          <t>297629</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>290571</t>
+          <t>286131</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>341892</t>
+          <t>341504</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>548245</t>
+          <t>548695</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>626170</t>
+          <t>626736</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50663</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>81570</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>69814</t>
+          <t>70370</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>105373</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>350764</t>
+          <t>356237</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>410282</t>
+          <t>412351</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318990</t>
+          <t>320385</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>377520</t>
+          <t>379412</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>687327</t>
+          <t>687058</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>769122</t>
+          <t>771588</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>305371</t>
+          <t>301488</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>361522</t>
+          <t>361134</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>426443</t>
+          <t>424667</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>484388</t>
+          <t>484456</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>746045</t>
+          <t>744033</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>829111</t>
+          <t>830345</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>431300</t>
+          <t>431703</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>514605</t>
+          <t>519223</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>229257</t>
+          <t>229103</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>628634</t>
+          <t>627137</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>727900</t>
+          <t>721698</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1650046</t>
+          <t>1643158</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1764295</t>
+          <t>1764424</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1647601</t>
+          <t>1643420</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1769596</t>
+          <t>1767983</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3335448</t>
+          <t>3329661</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3497079</t>
+          <t>3504877</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1159154</t>
+          <t>1156702</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1272711</t>
+          <t>1276134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1580306</t>
+          <t>1583138</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1702492</t>
+          <t>1705041</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2760102</t>
+          <t>2762130</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2926261</t>
+          <t>2936171</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56344</t>
+          <t>57245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94854</t>
+          <t>98939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22091</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39611</t>
+          <t>39175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84857</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129936</t>
+          <t>131189</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167294</t>
+          <t>167009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209385</t>
+          <t>208118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183829</t>
+          <t>183286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>208445</t>
+          <t>209785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>358722</t>
+          <t>357852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>408415</t>
+          <t>409320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36129</t>
+          <t>36246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66218</t>
+          <t>65825</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>53020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75205</t>
+          <t>74717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96682</t>
+          <t>96828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133467</t>
+          <t>132430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122055</t>
+          <t>118825</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174467</t>
+          <t>174869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>129603</t>
+          <t>128381</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165841</t>
+          <t>165422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260943</t>
+          <t>259773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326853</t>
+          <t>326544</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157204</t>
+          <t>157405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>216390</t>
+          <t>215707</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101075</t>
+          <t>100644</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136866</t>
+          <t>136892</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>270670</t>
+          <t>269454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341410</t>
+          <t>335132</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160976</t>
+          <t>162117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217434</t>
+          <t>216065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231407</t>
+          <t>231663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271399</t>
+          <t>271485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402243</t>
+          <t>407156</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>472039</t>
+          <t>475552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42970</t>
+          <t>43544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70942</t>
+          <t>71675</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26300</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46499</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74955</t>
+          <t>73387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109660</t>
+          <t>109439</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141371</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175354</t>
+          <t>177464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159278</t>
+          <t>158965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190071</t>
+          <t>189976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>310414</t>
+          <t>311793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>355776</t>
+          <t>356891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>85229</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117184</t>
+          <t>119346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124912</t>
+          <t>124341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>157138</t>
+          <t>153940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218692</t>
+          <t>219657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261052</t>
+          <t>263370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63004</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103155</t>
+          <t>101471</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72366</t>
+          <t>75135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100881</t>
+          <t>94356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169259</t>
+          <t>164209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102814</t>
+          <t>102894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143975</t>
+          <t>146233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>109643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>224151</t>
+          <t>224948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215094</t>
+          <t>214726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345895</t>
+          <t>348181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85540</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130748</t>
+          <t>130157</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185762</t>
+          <t>183254</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>336999</t>
+          <t>334741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>287197</t>
+          <t>288453</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>469679</t>
+          <t>472522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102267</t>
+          <t>103042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124220</t>
+          <t>124709</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>69069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157484</t>
+          <t>158966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159401</t>
+          <t>169063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272552</t>
+          <t>273979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>45634</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>65997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>35920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85577</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83719</t>
+          <t>83944</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142775</t>
+          <t>142435</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21227</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150049</t>
+          <t>149242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29857</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189892</t>
+          <t>176905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>49757</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>22665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39730</t>
+          <t>39524</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66925</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98997</t>
+          <t>98515</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>128228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99010</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123467</t>
+          <t>122416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>205350</t>
+          <t>202627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>244765</t>
+          <t>244127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -7577,12 +7577,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>104929</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>134962</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>118432</t>
+          <t>119314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143282</t>
+          <t>144291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231301</t>
+          <t>231849</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>270961</t>
+          <t>272574</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>191647</t>
+          <t>191880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>249740</t>
+          <t>250343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187998</t>
+          <t>185501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>577122</t>
+          <t>602524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>416249</t>
+          <t>414968</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>915166</t>
+          <t>894495</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>246802</t>
+          <t>245505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>306122</t>
+          <t>303913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>156371</t>
+          <t>131264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>384383</t>
+          <t>384984</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>339783</t>
+          <t>366931</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>662040</t>
+          <t>664414</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>108585</t>
+          <t>110283</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>154459</t>
+          <t>153975</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>114110</t>
+          <t>106052</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>288972</t>
+          <t>288799</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>210273</t>
+          <t>224633</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408048</t>
+          <t>408987</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -8263,12 +8263,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>64012</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>190614</t>
+          <t>193540</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51532</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>104385</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>217401</t>
+          <t>218476</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8348,12 +8348,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -8376,12 +8376,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>491699</t>
+          <t>487807</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>791802</t>
+          <t>780023</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8411,12 +8411,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>396991</t>
+          <t>397954</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>442819</t>
+          <t>441886</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>911851</t>
+          <t>913269</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1258973</t>
+          <t>1255543</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>83430</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>255034</t>
+          <t>256175</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>236341</t>
+          <t>235127</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>278249</t>
+          <t>280507</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>280559</t>
+          <t>278682</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>526235</t>
+          <t>528831</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>675876</t>
+          <t>660524</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>955381</t>
+          <t>949804</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>612920</t>
+          <t>614839</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1350506</t>
+          <t>1330069</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1445155</t>
+          <t>1448214</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2261008</t>
+          <t>2185213</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1553253</t>
+          <t>1552122</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2096743</t>
+          <t>2102696</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1248509</t>
+          <t>1251571</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1665732</t>
+          <t>1676566</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8902,12 +8902,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2975144</t>
+          <t>2979549</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3659953</t>
+          <t>3636724</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -8945,12 +8945,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>709136</t>
+          <t>695016</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>977738</t>
+          <t>982842</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8980,12 +8980,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1137216</t>
+          <t>1105479</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1515929</t>
+          <t>1503676</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1941472</t>
+          <t>1964527</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2457476</t>
+          <t>2459120</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IPAQ_MET-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73261</t>
+          <t>74703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106451</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>43436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>102199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139351</t>
+          <t>141335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120359</t>
+          <t>120518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156866</t>
+          <t>155493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140712</t>
+          <t>138929</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174482</t>
+          <t>174073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269238</t>
+          <t>269056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319292</t>
+          <t>318486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,68%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51924</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>82215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83523</t>
+          <t>84333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116595</t>
+          <t>117747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>144874</t>
+          <t>143355</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>189052</t>
+          <t>188552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53843</t>
+          <t>54355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>86545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76895</t>
+          <t>75675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114220</t>
+          <t>113916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>259021</t>
+          <t>257723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>303213</t>
+          <t>303252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249643</t>
+          <t>249860</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>299171</t>
+          <t>296453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>520358</t>
+          <t>523143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>589015</t>
+          <t>584307</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133447</t>
+          <t>134025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>172614</t>
+          <t>175260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202113</t>
+          <t>200968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248674</t>
+          <t>248659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345627</t>
+          <t>351615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409899</t>
+          <t>409436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>51306</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37590</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62945</t>
+          <t>62861</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164831</t>
+          <t>165908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200642</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179711</t>
+          <t>179127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>215398</t>
+          <t>215133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>353408</t>
+          <t>355369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>403801</t>
+          <t>403129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81987</t>
+          <t>81898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114754</t>
+          <t>112842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110681</t>
+          <t>109100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145478</t>
+          <t>145552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201151</t>
+          <t>201428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250115</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49143</t>
+          <t>47841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80288</t>
+          <t>77614</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>42506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>74832</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112276</t>
+          <t>111759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194228</t>
+          <t>196070</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234042</t>
+          <t>235258</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173168</t>
+          <t>174557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213418</t>
+          <t>215364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381636</t>
+          <t>382779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439587</t>
+          <t>439660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77311</t>
+          <t>76000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>111664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144100</t>
+          <t>142876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183545</t>
+          <t>182126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>227214</t>
+          <t>226484</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281960</t>
+          <t>280074</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>45026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25628</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63085</t>
+          <t>62050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74113</t>
+          <t>72691</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102191</t>
+          <t>101716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65955</t>
+          <t>64985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95300</t>
+          <t>93394</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>147766</t>
+          <t>148234</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188302</t>
+          <t>187696</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77938</t>
+          <t>77822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107155</t>
+          <t>106962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107114</t>
+          <t>108108</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136801</t>
+          <t>136820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192504</t>
+          <t>192631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>234589</t>
+          <t>235989</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38980</t>
+          <t>39088</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,12 +3026,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>24503</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>111933</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>144499</t>
+          <t>142823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110784</t>
+          <t>110105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>144185</t>
+          <t>141938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>229940</t>
+          <t>229439</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>275921</t>
+          <t>276504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>93025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>124295</t>
+          <t>124016</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3272,12 +3272,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115473</t>
+          <t>112946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148240</t>
+          <t>146271</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>215567</t>
+          <t>216903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>261189</t>
+          <t>262106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>74158</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>113967</t>
+          <t>111189</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62914</t>
+          <t>62917</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>116151</t>
+          <t>116470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>163578</t>
+          <t>162804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>267181</t>
+          <t>267061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>322340</t>
+          <t>321567</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>303691</t>
+          <t>304249</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>360780</t>
+          <t>357936</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>586004</t>
+          <t>586676</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>664961</t>
+          <t>662463</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>240925</t>
+          <t>246574</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>297629</t>
+          <t>299897</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>286131</t>
+          <t>286003</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>341504</t>
+          <t>339154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>548695</t>
+          <t>548814</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>626736</t>
+          <t>628110</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>50387</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>80509</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>70370</t>
+          <t>69853</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106432</t>
+          <t>106324</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>356237</t>
+          <t>353160</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>412351</t>
+          <t>408694</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>320385</t>
+          <t>320598</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>379412</t>
+          <t>378733</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>687058</t>
+          <t>687124</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>771588</t>
+          <t>772121</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>301488</t>
+          <t>303145</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>361134</t>
+          <t>358966</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>424667</t>
+          <t>423921</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>484456</t>
+          <t>483945</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>744033</t>
+          <t>749265</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>830345</t>
+          <t>827085</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>431703</t>
+          <t>433555</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>519223</t>
+          <t>516862</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>171304</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>229103</t>
+          <t>226488</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>627137</t>
+          <t>627220</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>721698</t>
+          <t>728740</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1643158</t>
+          <t>1651810</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1764424</t>
+          <t>1764368</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1643420</t>
+          <t>1649162</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1767983</t>
+          <t>1775590</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3329661</t>
+          <t>3334207</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3504877</t>
+          <t>3501877</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1156702</t>
+          <t>1155204</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1276134</t>
+          <t>1273174</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1583138</t>
+          <t>1575446</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1705041</t>
+          <t>1699591</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2762130</t>
+          <t>2770569</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2936171</t>
+          <t>2931303</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -5066,32 +5066,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>70809</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98939</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5136,32 +5136,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103831</t>
+          <t>102709</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>84333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131189</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -5179,32 +5179,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>188137</t>
+          <t>195294</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>167009</t>
+          <t>175982</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>208118</t>
+          <t>212758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195966</t>
+          <t>209887</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183286</t>
+          <t>195014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>209785</t>
+          <t>223221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5249,32 +5249,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>384102</t>
+          <t>405180</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>357852</t>
+          <t>384067</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>409320</t>
+          <t>428953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -5292,32 +5292,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>41250</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65825</t>
+          <t>66503</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5327,32 +5327,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64241</t>
+          <t>74274</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53020</t>
+          <t>62697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74717</t>
+          <t>87099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5362,32 +5362,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113144</t>
+          <t>127017</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96828</t>
+          <t>109909</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>132430</t>
+          <t>146740</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5405,17 +5405,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5475,17 +5475,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>146015</t>
+          <t>152863</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118825</t>
+          <t>130161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174869</t>
+          <t>179202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>146172</t>
+          <t>151928</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>128381</t>
+          <t>135538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>165422</t>
+          <t>172584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>292187</t>
+          <t>304791</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259773</t>
+          <t>271970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326544</t>
+          <t>337815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>184613</t>
+          <t>182226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157405</t>
+          <t>156672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>215707</t>
+          <t>213657</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>118003</t>
+          <t>123854</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100644</t>
+          <t>108280</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136892</t>
+          <t>143724</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>302616</t>
+          <t>306081</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>269454</t>
+          <t>271833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335132</t>
+          <t>342609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>187761</t>
+          <t>195558</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162117</t>
+          <t>167484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216065</t>
+          <t>222077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>250794</t>
+          <t>270712</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>231663</t>
+          <t>249570</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>271485</t>
+          <t>291592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>438555</t>
+          <t>466269</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>407156</t>
+          <t>427888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>475552</t>
+          <t>502835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55667</t>
+          <t>52748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>40104</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71675</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34747</t>
+          <t>35993</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45820</t>
+          <t>47034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>90414</t>
+          <t>88741</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73387</t>
+          <t>73887</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109439</t>
+          <t>105927</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>159335</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>142194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177464</t>
+          <t>177741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>174452</t>
+          <t>174660</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158965</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189976</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>333787</t>
+          <t>335242</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>311793</t>
+          <t>313898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>356891</t>
+          <t>358980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>101048</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85229</t>
+          <t>89121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119346</t>
+          <t>120592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>139929</t>
+          <t>145728</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124341</t>
+          <t>131447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153940</t>
+          <t>161986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>240977</t>
+          <t>248392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219657</t>
+          <t>225385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263370</t>
+          <t>269572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>98934</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62754</t>
+          <t>79599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>124390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>54124</t>
+          <t>63279</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33126</t>
+          <t>49441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>81126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135049</t>
+          <t>162214</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94356</t>
+          <t>134875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164209</t>
+          <t>189067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>123549</t>
+          <t>147752</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102894</t>
+          <t>124811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146233</t>
+          <t>173589</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>177659</t>
+          <t>199913</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109643</t>
+          <t>180731</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>224948</t>
+          <t>220381</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>301208</t>
+          <t>347666</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214726</t>
+          <t>318534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>348181</t>
+          <t>378988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108083</t>
+          <t>126458</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86895</t>
+          <t>101028</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>130157</t>
+          <t>151558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>243934</t>
+          <t>158768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>183254</t>
+          <t>140404</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>334741</t>
+          <t>179147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>352017</t>
+          <t>285227</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>288453</t>
+          <t>257624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>472522</t>
+          <t>314189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6890,32 +6890,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>114087</t>
+          <t>132637</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103042</t>
+          <t>120593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124709</t>
+          <t>143339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>124570</t>
+          <t>135531</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69069</t>
+          <t>124847</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158966</t>
+          <t>145249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6960,32 +6960,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>238657</t>
+          <t>268168</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169063</t>
+          <t>250375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273979</t>
+          <t>283260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -7003,32 +7003,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>62577</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45634</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>65997</t>
+          <t>74169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66324</t>
+          <t>72640</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35920</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>121264</t>
+          <t>135217</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83944</t>
+          <t>121109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>142435</t>
+          <t>152723</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -7116,32 +7116,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>17177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7151,32 +7151,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>67885</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149242</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7186,32 +7186,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>77600</t>
+          <t>31197</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176905</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -7229,17 +7229,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7264,17 +7264,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7299,17 +7299,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7346,32 +7346,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7381,32 +7381,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7416,32 +7416,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>52306</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39524</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66779</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -7459,32 +7459,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>112879</t>
+          <t>109553</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98515</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128228</t>
+          <t>123379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>110654</t>
+          <t>112350</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97568</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>122416</t>
+          <t>125158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>223533</t>
+          <t>221904</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202627</t>
+          <t>202413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>244127</t>
+          <t>241192</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -7572,32 +7572,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>119518</t>
+          <t>125304</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104929</t>
+          <t>111902</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134962</t>
+          <t>140233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>131336</t>
+          <t>136120</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119314</t>
+          <t>123230</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144291</t>
+          <t>149435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7642,32 +7642,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>250854</t>
+          <t>261424</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231849</t>
+          <t>243081</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>272574</t>
+          <t>283684</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -7685,17 +7685,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7755,17 +7755,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7802,32 +7802,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>220449</t>
+          <t>254563</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>191880</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>250343</t>
+          <t>288720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7837,32 +7837,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>351290</t>
+          <t>175610</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185501</t>
+          <t>155122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>602524</t>
+          <t>199227</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7872,32 +7872,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>571738</t>
+          <t>430172</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>414968</t>
+          <t>394779</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>894495</t>
+          <t>472328</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -7915,32 +7915,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>273892</t>
+          <t>311768</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>245505</t>
+          <t>279789</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>303913</t>
+          <t>341049</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7950,32 +7950,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>285431</t>
+          <t>347531</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131264</t>
+          <t>319922</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>384984</t>
+          <t>372826</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7985,32 +7985,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>559323</t>
+          <t>659299</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>366931</t>
+          <t>620881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>664414</t>
+          <t>700653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -8028,32 +8028,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>129938</t>
+          <t>153356</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>110283</t>
+          <t>131028</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153975</t>
+          <t>179631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8063,32 +8063,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>212544</t>
+          <t>248917</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>106052</t>
+          <t>225057</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>288799</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8098,32 +8098,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>342483</t>
+          <t>402273</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>224633</t>
+          <t>364776</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408987</t>
+          <t>439158</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -8141,17 +8141,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8211,17 +8211,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8258,32 +8258,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>134121</t>
+          <t>157805</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>64012</t>
+          <t>133419</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>193540</t>
+          <t>186861</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8293,32 +8293,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>53329</t>
+          <t>61437</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8328,32 +8328,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>174635</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>175020</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>218476</t>
+          <t>235162</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -8371,32 +8371,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>612487</t>
+          <t>434919</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>487807</t>
+          <t>405511</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>780023</t>
+          <t>466681</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8406,32 +8406,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>420709</t>
+          <t>487745</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>397954</t>
+          <t>461093</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>441886</t>
+          <t>513430</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8441,32 +8441,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>922664</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>913269</t>
+          <t>883018</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1255543</t>
+          <t>960662</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -8484,32 +8484,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>182113</t>
+          <t>205348</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>83430</t>
+          <t>181331</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>256175</t>
+          <t>228153</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8519,32 +8519,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>256507</t>
+          <t>296297</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>235127</t>
+          <t>271313</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>280507</t>
+          <t>320849</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8554,32 +8554,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>438620</t>
+          <t>501645</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>278682</t>
+          <t>468260</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>528831</t>
+          <t>539189</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -8597,17 +8597,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8632,17 +8632,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8667,17 +8667,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8714,32 +8714,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>862906</t>
+          <t>956209</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>660524</t>
+          <t>894221</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>949804</t>
+          <t>1016672</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8749,32 +8749,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>795913</t>
+          <t>656809</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>614839</t>
+          <t>614961</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1330069</t>
+          <t>698409</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8784,32 +8784,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1658818</t>
+          <t>1613018</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1448214</t>
+          <t>1533502</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2185213</t>
+          <t>1689215</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -8827,32 +8827,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1709833</t>
+          <t>1604671</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1552122</t>
+          <t>1535821</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2102696</t>
+          <t>1672184</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8862,32 +8862,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1549197</t>
+          <t>1728581</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1251571</t>
+          <t>1675636</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1676566</t>
+          <t>1783736</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8897,32 +8897,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3259029</t>
+          <t>3333252</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2979549</t>
+          <t>3244926</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3636724</t>
+          <t>3423196</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -8940,32 +8940,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>887079</t>
+          <t>971882</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>695016</t>
+          <t>915832</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>982842</t>
+          <t>1031606</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8975,32 +8975,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1367171</t>
+          <t>1351564</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1105479</t>
+          <t>1300256</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1503676</t>
+          <t>1402984</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9010,32 +9010,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2254249</t>
+          <t>2323446</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1964527</t>
+          <t>2242562</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2459120</t>
+          <t>2402306</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -9053,17 +9053,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9088,17 +9088,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
